--- a/Q_to_Boil/Q to Boil.xlsx
+++ b/Q_to_Boil/Q to Boil.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Q_to_Boil/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5098" documentId="8_{D10681A3-17E8-4E9B-B97D-DE7EC19F489E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE8F5AF4-7B4A-4C4D-BE97-2C02039244D2}"/>
+  <xr:revisionPtr revIDLastSave="6515" documentId="8_{D10681A3-17E8-4E9B-B97D-DE7EC19F489E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BD37389-D38E-4540-80C4-A6F45737EE98}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{663BD1A2-93FF-42B3-BC32-7BF716FE36A7}"/>
+    <workbookView xWindow="6345" yWindow="1125" windowWidth="21570" windowHeight="11295" xr2:uid="{663BD1A2-93FF-42B3-BC32-7BF716FE36A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -522,8 +522,8 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <f>fluid_mass*c_water*UNC_Fluid_C*(set_temp-ambient_temp+UNC_Fluid_Temp)</f>
-        <v>85132.684800000003</v>
+        <f>fluid_mass*c_water*UNC_Fluid_C*(set_temp-ambient_temp-UNC_Fluid_Temp)</f>
+        <v>64046.58</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
@@ -534,7 +534,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -545,7 +545,7 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>

--- a/Q_to_Boil/Q to Boil.xlsx
+++ b/Q_to_Boil/Q to Boil.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Q_to_Boil/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21010" documentId="8_{D10681A3-17E8-4E9B-B97D-DE7EC19F489E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B023C94D-C5E6-407E-B218-E6DF8DD8C8BA}"/>
+  <xr:revisionPtr revIDLastSave="52889" documentId="8_{D10681A3-17E8-4E9B-B97D-DE7EC19F489E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2165C33C-5876-434D-9CCA-433E3B9C435A}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{663BD1A2-93FF-42B3-BC32-7BF716FE36A7}"/>
   </bookViews>
@@ -478,7 +478,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>1.1775105975</v>
+        <v>0.58875</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
@@ -522,8 +522,8 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <f>fluid_mass*c_water*UNC_Fluid_C*(set_temp-ambient_temp+UNC_Fluid_Temp)</f>
-        <v>425667.25497081596</v>
+        <f>fluid_mass*c_water*UNC_Fluid_C*(set_temp-(ambient_temp+UNC_Fluid_Temp))</f>
+        <v>110849.84999999999</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
@@ -534,7 +534,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -545,7 +545,7 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>

--- a/Q_to_Boil/Q to Boil.xlsx
+++ b/Q_to_Boil/Q to Boil.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Q_to_Boil/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Q_to_Boil/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5758" documentId="8_{D10681A3-17E8-4E9B-B97D-DE7EC19F489E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EC24081-900C-4D97-BE9F-777344C04CBA}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="114_{AC40C6FF-ACCD-4A15-BBD0-51D09693BA08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F806EEC-B88F-447D-8607-4CA93A05795C}"/>
   <bookViews>
-    <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{663BD1A2-93FF-42B3-BC32-7BF716FE36A7}"/>
+    <workbookView xWindow="6795" yWindow="30" windowWidth="21570" windowHeight="11295" xr2:uid="{663BD1A2-93FF-42B3-BC32-7BF716FE36A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -474,7 +474,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.58874952899999999</v>
+        <v>0.5</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
@@ -519,7 +519,7 @@
       </c>
       <c r="B7">
         <f>fluid_mass*c_water*UNC_Fluid_C*(set_temp-ambient_temp+UNC_Fluid_Temp)</f>
-        <v>212831.54173463042</v>
+        <v>180748.80000000002</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>

--- a/Q_to_Boil/Q to Boil.xlsx
+++ b/Q_to_Boil/Q to Boil.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Q_to_Boil/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Q_to_Boil/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="114_{AC40C6FF-ACCD-4A15-BBD0-51D09693BA08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F806EEC-B88F-447D-8607-4CA93A05795C}"/>
+  <xr:revisionPtr revIDLastSave="36008" documentId="114_{AC40C6FF-ACCD-4A15-BBD0-51D09693BA08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D67BC91-2378-4D07-8C9E-EF9856461F8B}"/>
   <bookViews>
-    <workbookView xWindow="6795" yWindow="30" windowWidth="21570" windowHeight="11295" xr2:uid="{663BD1A2-93FF-42B3-BC32-7BF716FE36A7}"/>
+    <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{663BD1A2-93FF-42B3-BC32-7BF716FE36A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -139,6 +139,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -496,7 +500,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>25</v>
+        <v>0.994825152380023</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -518,8 +522,8 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <f>fluid_mass*c_water*UNC_Fluid_C*(set_temp-ambient_temp+UNC_Fluid_Temp)</f>
-        <v>180748.80000000002</v>
+        <f>fluid_mass*c_water*UNC_Fluid_C*(set_temp-UNC_Fluid_Temp)</f>
+        <v>105245.96800932635</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
@@ -530,7 +534,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>1.08</v>
+        <v>0.83285723267892098</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -541,7 +545,7 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>15</v>
+        <v>29.594953198208401</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>

--- a/Q_to_Boil/Q to Boil.xlsx
+++ b/Q_to_Boil/Q to Boil.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Q_to_Boil/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36008" documentId="114_{AC40C6FF-ACCD-4A15-BBD0-51D09693BA08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D67BC91-2378-4D07-8C9E-EF9856461F8B}"/>
+  <xr:revisionPtr revIDLastSave="40640" documentId="114_{AC40C6FF-ACCD-4A15-BBD0-51D09693BA08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9329A56C-B8B0-4C04-BEB3-4BE8C1A57F84}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{663BD1A2-93FF-42B3-BC32-7BF716FE36A7}"/>
   </bookViews>
@@ -500,7 +500,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.994825152380023</v>
+        <v>0.98955387225082103</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -523,7 +523,7 @@
       </c>
       <c r="B7">
         <f>fluid_mass*c_water*UNC_Fluid_C*(set_temp-UNC_Fluid_Temp)</f>
-        <v>105245.96800932635</v>
+        <v>144859.71667514346</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
@@ -534,7 +534,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>0.83285723267892098</v>
+        <v>0.93638494395187</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -545,7 +545,7 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>29.594953198208401</v>
+        <v>16.051132188182301</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>

--- a/Q_to_Boil/Q to Boil.xlsx
+++ b/Q_to_Boil/Q to Boil.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Q_to_Boil/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40640" documentId="114_{AC40C6FF-ACCD-4A15-BBD0-51D09693BA08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9329A56C-B8B0-4C04-BEB3-4BE8C1A57F84}"/>
+  <xr:revisionPtr revIDLastSave="40820" documentId="114_{AC40C6FF-ACCD-4A15-BBD0-51D09693BA08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54A2D71F-5B0F-4BB0-9947-AEF5B7F12A39}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{663BD1A2-93FF-42B3-BC32-7BF716FE36A7}"/>
   </bookViews>
@@ -500,7 +500,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.98955387225082103</v>
+        <v>1.04036007587084</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -523,7 +523,7 @@
       </c>
       <c r="B7">
         <f>fluid_mass*c_water*UNC_Fluid_C*(set_temp-UNC_Fluid_Temp)</f>
-        <v>144859.71667514346</v>
+        <v>110559.48984282692</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
@@ -534,7 +534,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>0.93638494395187</v>
+        <v>0.77327180416320795</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -545,7 +545,7 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>16.051132188182301</v>
+        <v>21.655720240608598</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>

--- a/Q_to_Boil/Q to Boil.xlsx
+++ b/Q_to_Boil/Q to Boil.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Q_to_Boil/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40820" documentId="114_{AC40C6FF-ACCD-4A15-BBD0-51D09693BA08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54A2D71F-5B0F-4BB0-9947-AEF5B7F12A39}"/>
+  <xr:revisionPtr revIDLastSave="42764" documentId="114_{AC40C6FF-ACCD-4A15-BBD0-51D09693BA08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C8D1DF0-EFB4-4998-82A4-4D7D3BF99E80}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{663BD1A2-93FF-42B3-BC32-7BF716FE36A7}"/>
   </bookViews>
@@ -500,7 +500,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1.04036007587084</v>
+        <v>0.98652107344169604</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -523,7 +523,7 @@
       </c>
       <c r="B7">
         <f>fluid_mass*c_water*UNC_Fluid_C*(set_temp-UNC_Fluid_Temp)</f>
-        <v>110559.48984282692</v>
+        <v>142160.53990600296</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
@@ -534,7 +534,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>0.77327180416320795</v>
+        <v>0.87193772566279704</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -545,7 +545,7 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>21.655720240608598</v>
+        <v>12.0651120144275</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>

--- a/Q_to_Boil/Q to Boil.xlsx
+++ b/Q_to_Boil/Q to Boil.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Q_to_Boil/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42764" documentId="114_{AC40C6FF-ACCD-4A15-BBD0-51D09693BA08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C8D1DF0-EFB4-4998-82A4-4D7D3BF99E80}"/>
+  <xr:revisionPtr revIDLastSave="48764" documentId="114_{AC40C6FF-ACCD-4A15-BBD0-51D09693BA08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11BC71A4-7D0B-4555-9931-1077216CCDA0}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{663BD1A2-93FF-42B3-BC32-7BF716FE36A7}"/>
   </bookViews>
@@ -500,7 +500,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.98652107344169604</v>
+        <v>0.99847613838737004</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -523,7 +523,7 @@
       </c>
       <c r="B7">
         <f>fluid_mass*c_water*UNC_Fluid_C*(set_temp-UNC_Fluid_Temp)</f>
-        <v>142160.53990600296</v>
+        <v>112830.95963596962</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
@@ -534,7 +534,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>0.87193772566279704</v>
+        <v>0.75153959587451802</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -545,7 +545,7 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>12.0651120144275</v>
+        <v>18.2346619793617</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
